--- a/Nifty_Futures_Index_Holiday_Behaviour_Master_2000_2026.xlsx
+++ b/Nifty_Futures_Index_Holiday_Behaviour_Master_2000_2026.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive_Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upcoming_Playbook_2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Complete_26Y_Trade_Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diwali (Laxmi Pujan and Balipr" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ganesh Chaturthi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christmas and Year-End" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ganesh Chaturthi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christmas and Year-End" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diwali (Laxmi Pujan and Balipr" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shri Ram Navami" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bakri Id (Id-Ul-Adha)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Good Friday" sheetId="9" state="visible" r:id="rId9"/>
@@ -711,17 +711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Diwali (Laxmi Pujan &amp; Balipratipada)</t>
+          <t>Ganesh Chaturthi</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Festival of Lights</t>
+          <t>Festive Accumulation</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-7 to T+5</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -730,28 +730,28 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>88.45999999999999</v>
+        <v>88</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>2.07</v>
+        <v>3.42</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>139.25</v>
+        <v>175.63</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>3620.55</v>
+        <v>4390.7</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -760,17 +760,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Ganesh Chaturthi</t>
+          <t>Christmas &amp; Year-End</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Festive Accumulation</t>
+          <t>Year-End Season</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>T-7 to T+5</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="F6" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>22</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>175.63</v>
+        <v>151.06</v>
       </c>
       <c r="L6" s="15" t="n">
-        <v>4390.7</v>
+        <v>3927.65</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>7.5</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -809,17 +809,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Christmas &amp; Year-End</t>
+          <t>Diwali (Laxmi Pujan &amp; Balipratipada)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Year-End Season</t>
+          <t>Festival of Lights</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -840,16 +840,16 @@
         <v>84.62</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>151.06</v>
+        <v>147.65</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3927.65</v>
+        <v>3838.85</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>22.72</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1085,16 +1085,16 @@
         <v>73.08</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>183.73</v>
+        <v>124.01</v>
       </c>
       <c r="L12" s="15" t="n">
-        <v>4777.05</v>
+        <v>3224.15</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>3.39</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1348,47 +1348,47 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Dussehra / Vijayadashami</t>
+          <t>Maharashtra Day</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Festive Accumulation</t>
+          <t>State &amp; Labour Day</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>NIFTY SHORT</t>
+          <t>T-8 to T+1</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>NIFTY LONG</t>
         </is>
       </c>
       <c r="F18" s="11" t="n">
         <v>26</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>53</v>
+        <v>127.98</v>
       </c>
       <c r="L18" s="15" t="n">
-        <v>1378.1</v>
+        <v>3327.45</v>
       </c>
       <c r="M18" s="16" t="n">
-        <v>1.78</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1397,47 +1397,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Holi Festival</t>
+          <t>Dussehra / Vijayadashami</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Festive Accumulation</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+6</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>NIFTY LONG</t>
+          <t>T-8 to T+4</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY SHORT</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>-0.13</v>
+        <v>0.57</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.53</v>
+        <v>125.92</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>13.2</v>
+        <v>3273.9</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>1</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Maharashtra Day</t>
+          <t>Holi Festival</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>State &amp; Labour Day</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>T-8 to T+1</t>
+          <t>T-1 to T+6</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1477,16 +1477,16 @@
         <v>65.38</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1.23</v>
+        <v>-0.34</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>127.98</v>
+        <v>-53.32</v>
       </c>
       <c r="L20" s="15" t="n">
-        <v>3327.45</v>
+        <v>-1386.3</v>
       </c>
       <c r="M20" s="16" t="n">
-        <v>7.23</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1637,12 +1637,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Diwali (Laxmi Pujan &amp; Balipratipada)</t>
+          <t>Ganesh Chaturthi</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>21-Oct-2026 (Wed)</t>
+          <t>14-Sep-2026 (Mon)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-7 to T+5</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026 (Tue)</t>
+          <t>03-Sep-2026 (Thu)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1666,32 +1666,32 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>88.45999999999999</v>
+        <v>88</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>2.07</v>
+        <v>3.42</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>139.25</v>
+        <v>175.63</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K4" s="18" t="inlineStr">
         <is>
-          <t>Samvat New Year Muhurat trading, festive demand surge &amp; pre-Diwali run-up</t>
+          <t>Ganesh Utsav festive shopping, automobile sales surge &amp; Q2 ending momentum</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Ganesh Chaturthi</t>
+          <t>Christmas &amp; Year-End</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>14-Sep-2026 (Mon)</t>
+          <t>25-Dec-2026 (Fri)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1701,46 +1701,46 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>T-7 to T+5</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>02-Sep-2026 (Wed)</t>
+          <t>24-Dec-2026 (Thu)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>21-Sep-2026 (Mon)</t>
+          <t>05-Jan-2027 (Tue)</t>
         </is>
       </c>
       <c r="G5" s="13" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>175.63</v>
+        <v>151.06</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K5" s="19" t="inlineStr">
         <is>
-          <t>Ganesh Utsav festive shopping, automobile sales surge &amp; Q2 ending momentum</t>
+          <t>FII book closing, global liquidity contraction &amp; tax-loss harvesting play</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Christmas &amp; Year-End</t>
+          <t>Diwali (Laxmi Pujan &amp; Balipratipada)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>25-Dec-2026 (Fri)</t>
+          <t>08-Nov-2026 (Sun)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1750,34 +1750,34 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>18-Sep-2026 (Fri)</t>
+          <t>02-Nov-2026 (Mon)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026 (Mon)</t>
+          <t>13-Nov-2026 (Fri)</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
         <v>84.62</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>151.06</v>
+        <v>147.65</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
-          <t>FII book closing, global liquidity contraction &amp; tax-loss harvesting play</t>
+          <t>Samvat New Year Muhurat trading, festive demand surge &amp; pre-Diwali run-up</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>24-Mar-2026 (Tue)</t>
+          <t>25-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>18-May-2026 (Mon)</t>
+          <t>19-May-2026 (Tue)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>25-Mar-2026 (Wed)</t>
+          <t>27-Mar-2026 (Fri)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>25-Mar-2026 (Wed)</t>
+          <t>27-Mar-2026 (Fri)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>03-Mar-2026 (Tue)</t>
+          <t>15-Feb-2026 (Sun)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2000,22 +2000,22 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>20-Feb-2026 (Fri)</t>
+          <t>06-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>24-Feb-2026 (Tue)</t>
         </is>
       </c>
       <c r="G11" s="13" t="n">
         <v>73.08</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>183.73</v>
+        <v>124.01</v>
       </c>
       <c r="J11" s="11" t="n">
         <v>7</v>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026 (Tue)</t>
+          <t>12-Nov-2026 (Thu)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026 (Mon)</t>
+          <t>01-Dec-2026 (Tue)</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>13-Aug-2026 (Thu)</t>
+          <t>14-Aug-2026 (Fri)</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026 (Tue)</t>
+          <t>28-Sep-2026 (Mon)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026 (Mon)</t>
+          <t>13-Oct-2026 (Tue)</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>30-Mar-2026 (Mon)</t>
+          <t>01-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>12-Jan-2026 (Mon)</t>
+          <t>13-Jan-2026 (Tue)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2274,110 +2274,110 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Dussehra / Vijayadashami</t>
+          <t>Maharashtra Day</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>20-Oct-2026 (Tue)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>NIFTY SHORT</t>
+          <t>01-May-2026 (Fri)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>NIFTY LONG</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+1</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026 (Thu)</t>
+          <t>21-Apr-2026 (Tue)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>21-Sep-2026 (Mon)</t>
+          <t>04-May-2026 (Mon)</t>
         </is>
       </c>
       <c r="G17" s="13" t="n">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>53</v>
+        <v>127.98</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K17" s="19" t="inlineStr">
         <is>
-          <t>Navratri into Vijayadashami festive momentum &amp; seasonal liquidity injection</t>
+          <t>May series opening accumulation &amp; start of Q4 corporate earnings peak</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Holi Festival</t>
+          <t>Dussehra / Vijayadashami</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>14-Mar-2026 (Sat)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>NIFTY LONG</t>
+          <t>20-Oct-2026 (Tue)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>NIFTY SHORT</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+6</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>08-Oct-2026 (Thu)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>23-Mar-2026 (Mon)</t>
+          <t>26-Oct-2026 (Mon)</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>-0.13</v>
+        <v>0.57</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0.53</v>
+        <v>125.92</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>Spring festival consumption surge and pre-Holi equity momentum</t>
+          <t>Navratri into Vijayadashami festive momentum &amp; seasonal liquidity injection</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Maharashtra Day</t>
+          <t>Holi Festival</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>01-May-2026 (Fri)</t>
+          <t>03-Mar-2026 (Tue)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -2387,34 +2387,34 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>T-8 to T+1</t>
+          <t>T-1 to T+6</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>20-Apr-2026 (Mon)</t>
+          <t>02-Mar-2026 (Mon)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>04-May-2026 (Mon)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="G19" s="13" t="n">
         <v>65.38</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>1.23</v>
+        <v>-0.34</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>127.98</v>
+        <v>-53.32</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K19" s="19" t="inlineStr">
         <is>
-          <t>May series opening accumulation &amp; start of Q4 corporate earnings peak</t>
+          <t>Spring festival consumption surge and pre-Holi equity momentum</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>22-Jun-2026 (Mon)</t>
+          <t>23-Jun-2026 (Tue)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N439"/>
+  <dimension ref="A1:N440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2720,33 +2720,33 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27-Sep-2000 (Wed)</t>
+          <t>25-Sep-2000 (Mon)</t>
         </is>
       </c>
       <c r="H6" s="20" t="n">
-        <v>1294.9</v>
+        <v>1293.35</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>11-Oct-2000 (Wed)</t>
+          <t>13-Oct-2000 (Fri)</t>
         </is>
       </c>
       <c r="J6" s="20" t="n">
-        <v>1210.4</v>
+        <v>1184.75</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>84.5</v>
+        <v>108.6</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6.53</v>
+        <v>8.4</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>2112.5</v>
+        <v>2715</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -2778,33 +2778,33 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>23-Oct-2000 (Mon)</t>
+          <t>20-Oct-2000 (Fri)</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>1144.9</v>
+        <v>1138.85</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>01-Nov-2000 (Wed)</t>
+          <t>02-Nov-2000 (Thu)</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
-        <v>1207.6</v>
+        <v>1230.8</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>62.7</v>
+        <v>91.95</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>5.48</v>
+        <v>8.07</v>
       </c>
       <c r="M7" s="23" t="n">
-        <v>1567.5</v>
+        <v>2298.75</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -3706,37 +3706,37 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>17-Oct-2001 (Wed)</t>
+          <t>15-Oct-2001 (Mon)</t>
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>970.25</v>
+        <v>944.95</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>30-Oct-2001 (Tue)</t>
+          <t>01-Nov-2001 (Thu)</t>
         </is>
       </c>
       <c r="J23" s="22" t="n">
-        <v>950</v>
+        <v>981.4</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>20.25</v>
+        <v>-36.45</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>2.09</v>
+        <v>-3.86</v>
       </c>
       <c r="M23" s="23" t="n">
-        <v>506.25</v>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-911.25</v>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3764,33 +3764,33 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>09-Nov-2001 (Fri)</t>
+          <t>08-Nov-2001 (Thu)</t>
         </is>
       </c>
       <c r="H24" s="20" t="n">
-        <v>990.05</v>
+        <v>988.3</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>21-Nov-2001 (Wed)</t>
+          <t>22-Nov-2001 (Thu)</t>
         </is>
       </c>
       <c r="J24" s="20" t="n">
-        <v>1053.85</v>
+        <v>1057.5</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>63.8</v>
+        <v>69.2</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>6.44</v>
+        <v>7</v>
       </c>
       <c r="M24" s="21" t="n">
-        <v>1595</v>
+        <v>1730</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -4692,33 +4692,33 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>03-Oct-2002 (Thu)</t>
+          <t>30-Sep-2002 (Mon)</t>
         </is>
       </c>
       <c r="H40" s="20" t="n">
-        <v>952.4</v>
+        <v>957.75</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>17-Oct-2002 (Thu)</t>
+          <t>21-Oct-2002 (Mon)</t>
         </is>
       </c>
       <c r="J40" s="20" t="n">
-        <v>975.85</v>
+        <v>968.15</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>-23.45</v>
+        <v>-10.4</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>-2.46</v>
+        <v>-1.09</v>
       </c>
       <c r="M40" s="21" t="n">
-        <v>-586.25</v>
+        <v>-260</v>
       </c>
       <c r="N40" s="17" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>2002-11-06</t>
+          <t>2002-11-04</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -4750,16 +4750,16 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>30-Oct-2002 (Wed)</t>
+          <t>28-Oct-2002 (Mon)</t>
         </is>
       </c>
       <c r="H41" s="22" t="n">
-        <v>938.4</v>
+        <v>927.7</v>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
@@ -4770,13 +4770,13 @@
         <v>955.55</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>17.15</v>
+        <v>27.85</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="M41" s="23" t="n">
-        <v>428.75</v>
+        <v>696.25</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
@@ -5678,33 +5678,33 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>24-Sep-2003 (Wed)</t>
+          <t>22-Sep-2003 (Mon)</t>
         </is>
       </c>
       <c r="H57" s="22" t="n">
-        <v>1371.9</v>
+        <v>1299.65</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>07-Oct-2003 (Tue)</t>
+          <t>09-Oct-2003 (Thu)</t>
         </is>
       </c>
       <c r="J57" s="22" t="n">
-        <v>1475.2</v>
+        <v>1506.5</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>-103.3</v>
+        <v>-206.85</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>-7.53</v>
+        <v>-15.92</v>
       </c>
       <c r="M57" s="23" t="n">
-        <v>-2582.5</v>
+        <v>-5171.25</v>
       </c>
       <c r="N57" s="17" t="inlineStr">
         <is>
@@ -5736,33 +5736,33 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>21-Oct-2003 (Tue)</t>
+          <t>20-Oct-2003 (Mon)</t>
         </is>
       </c>
       <c r="H58" s="20" t="n">
-        <v>1510.7</v>
+        <v>1541.4</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>30-Oct-2003 (Thu)</t>
+          <t>31-Oct-2003 (Fri)</t>
         </is>
       </c>
       <c r="J58" s="20" t="n">
-        <v>1517.5</v>
+        <v>1559.45</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>6.8</v>
+        <v>18.05</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>0.45</v>
+        <v>1.17</v>
       </c>
       <c r="M58" s="21" t="n">
-        <v>170</v>
+        <v>451.25</v>
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
@@ -6664,33 +6664,33 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>12-Oct-2004 (Tue)</t>
+          <t>08-Oct-2004 (Fri)</t>
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>1785.8</v>
+        <v>1817.65</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>26-Oct-2004 (Tue)</t>
+          <t>28-Oct-2004 (Thu)</t>
         </is>
       </c>
       <c r="J74" s="20" t="n">
-        <v>1782.9</v>
+        <v>1800.55</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.9</v>
+        <v>17.1</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>0.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M74" s="21" t="n">
-        <v>72.5</v>
+        <v>427.5</v>
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>2004-11-15</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -6722,33 +6722,33 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>08-Nov-2004 (Mon)</t>
+          <t>05-Nov-2004 (Fri)</t>
         </is>
       </c>
       <c r="H75" s="22" t="n">
-        <v>1862.05</v>
+        <v>1856.8</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>18-Nov-2004 (Thu)</t>
+          <t>19-Nov-2004 (Fri)</t>
         </is>
       </c>
       <c r="J75" s="22" t="n">
-        <v>1894.9</v>
+        <v>1871.3</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>32.85</v>
+        <v>14.5</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>1.76</v>
+        <v>0.78</v>
       </c>
       <c r="M75" s="23" t="n">
-        <v>821.25</v>
+        <v>362.5</v>
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
@@ -7650,33 +7650,33 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>03-Oct-2005 (Mon)</t>
+          <t>29-Sep-2005 (Thu)</t>
         </is>
       </c>
       <c r="H91" s="22" t="n">
-        <v>2627.2</v>
+        <v>2612.5</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>14-Oct-2005 (Fri)</t>
+          <t>18-Oct-2005 (Tue)</t>
         </is>
       </c>
       <c r="J91" s="22" t="n">
-        <v>2486.5</v>
+        <v>2460.95</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>140.7</v>
+        <v>151.55</v>
       </c>
       <c r="L91" s="14" t="n">
-        <v>5.36</v>
+        <v>5.8</v>
       </c>
       <c r="M91" s="23" t="n">
-        <v>3517.5</v>
+        <v>3788.75</v>
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
@@ -7708,33 +7708,33 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>27-Oct-2005 (Thu)</t>
+          <t>26-Oct-2005 (Wed)</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>2361.1</v>
+        <v>2413.65</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>09-Nov-2005 (Wed)</t>
+          <t>10-Nov-2005 (Thu)</t>
         </is>
       </c>
       <c r="J92" s="20" t="n">
-        <v>2480.75</v>
+        <v>2489.95</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>119.65</v>
+        <v>76.3</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>5.07</v>
+        <v>3.16</v>
       </c>
       <c r="M92" s="21" t="n">
-        <v>2991.25</v>
+        <v>1907.5</v>
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
@@ -8636,37 +8636,37 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2006 (Thu)</t>
+          <t>19-Sep-2006 (Tue)</t>
         </is>
       </c>
       <c r="H108" s="20" t="n">
-        <v>3556.85</v>
+        <v>3447.95</v>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>04-Oct-2006 (Wed)</t>
+          <t>06-Oct-2006 (Fri)</t>
         </is>
       </c>
       <c r="J108" s="20" t="n">
-        <v>3519.2</v>
+        <v>3573.95</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>37.65</v>
+        <v>-126</v>
       </c>
       <c r="L108" s="8" t="n">
-        <v>1.06</v>
+        <v>-3.65</v>
       </c>
       <c r="M108" s="21" t="n">
-        <v>941.25</v>
-      </c>
-      <c r="N108" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-3150</v>
+      </c>
+      <c r="N108" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-10-21</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -8694,16 +8694,16 @@
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>17-Oct-2006 (Tue)</t>
+          <t>13-Oct-2006 (Fri)</t>
         </is>
       </c>
       <c r="H109" s="22" t="n">
-        <v>3719.1</v>
+        <v>3678.4</v>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
@@ -8714,13 +8714,13 @@
         <v>3775.1</v>
       </c>
       <c r="K109" s="15" t="n">
-        <v>56</v>
+        <v>96.7</v>
       </c>
       <c r="L109" s="14" t="n">
-        <v>1.51</v>
+        <v>2.63</v>
       </c>
       <c r="M109" s="23" t="n">
-        <v>1400</v>
+        <v>2417.5</v>
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
@@ -9564,37 +9564,37 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>11-Oct-2007 (Thu)</t>
+          <t>09-Oct-2007 (Tue)</t>
         </is>
       </c>
       <c r="H124" s="20" t="n">
-        <v>5545.05</v>
+        <v>5336.5</v>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2007 (Tue)</t>
+          <t>25-Oct-2007 (Thu)</t>
         </is>
       </c>
       <c r="J124" s="20" t="n">
-        <v>5489.1</v>
+        <v>5573.4</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>55.95</v>
+        <v>-236.9</v>
       </c>
       <c r="L124" s="8" t="n">
-        <v>1.01</v>
+        <v>-4.44</v>
       </c>
       <c r="M124" s="21" t="n">
-        <v>1398.75</v>
-      </c>
-      <c r="N124" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-5922.5</v>
+      </c>
+      <c r="N124" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9622,33 +9622,33 @@
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>06-Nov-2007 (Tue)</t>
+          <t>05-Nov-2007 (Mon)</t>
         </is>
       </c>
       <c r="H125" s="22" t="n">
-        <v>5802.25</v>
+        <v>5844.9</v>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>15-Nov-2007 (Thu)</t>
+          <t>16-Nov-2007 (Fri)</t>
         </is>
       </c>
       <c r="J125" s="22" t="n">
-        <v>5915.9</v>
+        <v>5913.55</v>
       </c>
       <c r="K125" s="15" t="n">
-        <v>113.65</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="L125" s="14" t="n">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="M125" s="23" t="n">
-        <v>2841.25</v>
+        <v>1716.25</v>
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
@@ -10550,33 +10550,33 @@
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>29-Sep-2008 (Mon)</t>
+          <t>25-Sep-2008 (Thu)</t>
         </is>
       </c>
       <c r="H141" s="22" t="n">
-        <v>3859.4</v>
+        <v>4115.35</v>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>13-Oct-2008 (Mon)</t>
+          <t>15-Oct-2008 (Wed)</t>
         </is>
       </c>
       <c r="J141" s="22" t="n">
-        <v>3534.1</v>
+        <v>3342.8</v>
       </c>
       <c r="K141" s="15" t="n">
-        <v>325.3</v>
+        <v>772.55</v>
       </c>
       <c r="L141" s="14" t="n">
-        <v>8.43</v>
+        <v>18.77</v>
       </c>
       <c r="M141" s="23" t="n">
-        <v>8132.5</v>
+        <v>19313.75</v>
       </c>
       <c r="N141" s="6" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>2008-10-30</t>
+          <t>2008-10-28</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -10608,16 +10608,16 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2008 (Thu)</t>
+          <t>21-Oct-2008 (Tue)</t>
         </is>
       </c>
       <c r="H142" s="20" t="n">
-        <v>2934.7</v>
+        <v>3241.95</v>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
@@ -10628,17 +10628,17 @@
         <v>3161.9</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>227.2</v>
+        <v>-80.05</v>
       </c>
       <c r="L142" s="8" t="n">
-        <v>7.74</v>
+        <v>-2.47</v>
       </c>
       <c r="M142" s="21" t="n">
-        <v>5680</v>
-      </c>
-      <c r="N142" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-2001.25</v>
+      </c>
+      <c r="N142" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -11420,33 +11420,33 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2009 (Wed)</t>
+          <t>14-Sep-2009 (Mon)</t>
         </is>
       </c>
       <c r="H156" s="20" t="n">
-        <v>4961.85</v>
+        <v>4822</v>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>30-Sep-2009 (Wed)</t>
+          <t>05-Oct-2009 (Mon)</t>
         </is>
       </c>
       <c r="J156" s="20" t="n">
-        <v>5073.55</v>
+        <v>5008.5</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>-111.7</v>
+        <v>-186.5</v>
       </c>
       <c r="L156" s="8" t="n">
-        <v>-2.25</v>
+        <v>-3.87</v>
       </c>
       <c r="M156" s="21" t="n">
-        <v>-2792.5</v>
+        <v>-4662.5</v>
       </c>
       <c r="N156" s="17" t="inlineStr">
         <is>
@@ -11536,33 +11536,33 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>09-Oct-2009 (Fri)</t>
+          <t>08-Oct-2009 (Thu)</t>
         </is>
       </c>
       <c r="H158" s="20" t="n">
-        <v>4934.5</v>
+        <v>5001.7</v>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>22-Oct-2009 (Thu)</t>
+          <t>23-Oct-2009 (Fri)</t>
         </is>
       </c>
       <c r="J158" s="20" t="n">
-        <v>4997.4</v>
+        <v>5007.9</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>62.9</v>
+        <v>6.2</v>
       </c>
       <c r="L158" s="8" t="n">
-        <v>1.27</v>
+        <v>0.12</v>
       </c>
       <c r="M158" s="21" t="n">
-        <v>1572.5</v>
+        <v>155</v>
       </c>
       <c r="N158" s="6" t="inlineStr">
         <is>
@@ -12464,33 +12464,33 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>07-Oct-2010 (Thu)</t>
+          <t>05-Oct-2010 (Tue)</t>
         </is>
       </c>
       <c r="H174" s="20" t="n">
-        <v>6146.85</v>
+        <v>6182.85</v>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>19-Oct-2010 (Tue)</t>
+          <t>21-Oct-2010 (Thu)</t>
         </is>
       </c>
       <c r="J174" s="20" t="n">
-        <v>6044.15</v>
+        <v>6135.15</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>102.7</v>
+        <v>47.7</v>
       </c>
       <c r="L174" s="8" t="n">
-        <v>1.67</v>
+        <v>0.77</v>
       </c>
       <c r="M174" s="21" t="n">
-        <v>2567.5</v>
+        <v>1192.5</v>
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
@@ -12522,33 +12522,33 @@
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>01-Nov-2010 (Mon)</t>
+          <t>29-Oct-2010 (Fri)</t>
         </is>
       </c>
       <c r="H175" s="22" t="n">
-        <v>6152.05</v>
+        <v>6043.6</v>
       </c>
       <c r="I175" s="11" t="inlineStr">
         <is>
-          <t>10-Nov-2010 (Wed)</t>
+          <t>11-Nov-2010 (Thu)</t>
         </is>
       </c>
       <c r="J175" s="22" t="n">
-        <v>6308.3</v>
+        <v>6232.55</v>
       </c>
       <c r="K175" s="15" t="n">
-        <v>156.25</v>
+        <v>188.95</v>
       </c>
       <c r="L175" s="14" t="n">
-        <v>2.54</v>
+        <v>3.13</v>
       </c>
       <c r="M175" s="23" t="n">
-        <v>3906.25</v>
+        <v>4723.75</v>
       </c>
       <c r="N175" s="6" t="inlineStr">
         <is>
@@ -13450,33 +13450,33 @@
       </c>
       <c r="F191" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>27-Sep-2011 (Tue)</t>
+          <t>23-Sep-2011 (Fri)</t>
         </is>
       </c>
       <c r="H191" s="22" t="n">
-        <v>4977.85</v>
+        <v>4870.7</v>
       </c>
       <c r="I191" s="11" t="inlineStr">
         <is>
-          <t>10-Oct-2011 (Mon)</t>
+          <t>12-Oct-2011 (Wed)</t>
         </is>
       </c>
       <c r="J191" s="22" t="n">
-        <v>4993.3</v>
+        <v>5112.85</v>
       </c>
       <c r="K191" s="15" t="n">
-        <v>-15.45</v>
+        <v>-242.15</v>
       </c>
       <c r="L191" s="14" t="n">
-        <v>-0.31</v>
+        <v>-4.97</v>
       </c>
       <c r="M191" s="23" t="n">
-        <v>-386.25</v>
+        <v>-6053.75</v>
       </c>
       <c r="N191" s="17" t="inlineStr">
         <is>
@@ -13508,33 +13508,33 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>20-Oct-2011 (Thu)</t>
+          <t>19-Oct-2011 (Wed)</t>
         </is>
       </c>
       <c r="H192" s="20" t="n">
-        <v>5102.85</v>
+        <v>5149.4</v>
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>01-Nov-2011 (Tue)</t>
+          <t>02-Nov-2011 (Wed)</t>
         </is>
       </c>
       <c r="J192" s="20" t="n">
-        <v>5291.4</v>
+        <v>5280.2</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>188.55</v>
+        <v>130.8</v>
       </c>
       <c r="L192" s="8" t="n">
-        <v>3.69</v>
+        <v>2.54</v>
       </c>
       <c r="M192" s="21" t="n">
-        <v>4713.75</v>
+        <v>3270</v>
       </c>
       <c r="N192" s="6" t="inlineStr">
         <is>
@@ -14436,33 +14436,33 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>15-Oct-2012 (Mon)</t>
+          <t>11-Oct-2012 (Thu)</t>
         </is>
       </c>
       <c r="H208" s="20" t="n">
-        <v>5702.75</v>
+        <v>5739.35</v>
       </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
-          <t>26-Oct-2012 (Fri)</t>
+          <t>30-Oct-2012 (Tue)</t>
         </is>
       </c>
       <c r="J208" s="20" t="n">
-        <v>5699.3</v>
+        <v>5628</v>
       </c>
       <c r="K208" s="9" t="n">
-        <v>3.45</v>
+        <v>111.35</v>
       </c>
       <c r="L208" s="8" t="n">
-        <v>0.06</v>
+        <v>1.94</v>
       </c>
       <c r="M208" s="21" t="n">
-        <v>86.25</v>
+        <v>2783.75</v>
       </c>
       <c r="N208" s="6" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>2012-11-14</t>
+          <t>2012-11-13</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -14552,33 +14552,33 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>07-Nov-2012 (Wed)</t>
+          <t>06-Nov-2012 (Tue)</t>
         </is>
       </c>
       <c r="H210" s="20" t="n">
-        <v>5793.25</v>
+        <v>5766.65</v>
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>19-Nov-2012 (Mon)</t>
+          <t>20-Nov-2012 (Tue)</t>
         </is>
       </c>
       <c r="J210" s="20" t="n">
-        <v>5589.65</v>
+        <v>5583.85</v>
       </c>
       <c r="K210" s="9" t="n">
-        <v>-203.6</v>
+        <v>-182.8</v>
       </c>
       <c r="L210" s="8" t="n">
-        <v>-3.51</v>
+        <v>-3.17</v>
       </c>
       <c r="M210" s="21" t="n">
-        <v>-5090</v>
+        <v>-4570</v>
       </c>
       <c r="N210" s="17" t="inlineStr">
         <is>
@@ -15422,33 +15422,33 @@
       </c>
       <c r="F225" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>01-Oct-2013 (Tue)</t>
+          <t>27-Sep-2013 (Fri)</t>
         </is>
       </c>
       <c r="H225" s="22" t="n">
-        <v>5828.45</v>
+        <v>5888.15</v>
       </c>
       <c r="I225" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2013 (Tue)</t>
+          <t>18-Oct-2013 (Fri)</t>
         </is>
       </c>
       <c r="J225" s="22" t="n">
-        <v>6110.65</v>
+        <v>6210.45</v>
       </c>
       <c r="K225" s="15" t="n">
-        <v>-282.2</v>
+        <v>-322.3</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>-4.84</v>
+        <v>-5.47</v>
       </c>
       <c r="M225" s="23" t="n">
-        <v>-7055</v>
+        <v>-8057.5</v>
       </c>
       <c r="N225" s="17" t="inlineStr">
         <is>
@@ -15538,33 +15538,33 @@
       </c>
       <c r="F227" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G227" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2013 (Mon)</t>
+          <t>25-Oct-2013 (Fri)</t>
         </is>
       </c>
       <c r="H227" s="22" t="n">
-        <v>6105.3</v>
+        <v>6151.55</v>
       </c>
       <c r="I227" s="11" t="inlineStr">
         <is>
-          <t>07-Nov-2013 (Thu)</t>
+          <t>08-Nov-2013 (Fri)</t>
         </is>
       </c>
       <c r="J227" s="22" t="n">
-        <v>6227.3</v>
+        <v>6186.6</v>
       </c>
       <c r="K227" s="15" t="n">
-        <v>122</v>
+        <v>35.05</v>
       </c>
       <c r="L227" s="14" t="n">
-        <v>2</v>
+        <v>0.57</v>
       </c>
       <c r="M227" s="23" t="n">
-        <v>3050</v>
+        <v>876.25</v>
       </c>
       <c r="N227" s="6" t="inlineStr">
         <is>
@@ -16408,33 +16408,33 @@
       </c>
       <c r="F242" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>23-Sep-2014 (Tue)</t>
+          <t>19-Sep-2014 (Fri)</t>
         </is>
       </c>
       <c r="H242" s="20" t="n">
-        <v>8032.2</v>
+        <v>8131</v>
       </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
-          <t>08-Oct-2014 (Wed)</t>
+          <t>10-Oct-2014 (Fri)</t>
         </is>
       </c>
       <c r="J242" s="20" t="n">
-        <v>7895.5</v>
+        <v>7886.8</v>
       </c>
       <c r="K242" s="9" t="n">
-        <v>136.7</v>
+        <v>244.2</v>
       </c>
       <c r="L242" s="8" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="M242" s="21" t="n">
-        <v>3417.5</v>
+        <v>6105</v>
       </c>
       <c r="N242" s="6" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2014-10-23</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -16524,33 +16524,33 @@
       </c>
       <c r="F244" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>17-Oct-2014 (Fri)</t>
+          <t>16-Oct-2014 (Thu)</t>
         </is>
       </c>
       <c r="H244" s="20" t="n">
-        <v>7817.05</v>
+        <v>7778.1</v>
       </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
-          <t>29-Oct-2014 (Wed)</t>
+          <t>30-Oct-2014 (Thu)</t>
         </is>
       </c>
       <c r="J244" s="20" t="n">
-        <v>8089.15</v>
+        <v>8166.6</v>
       </c>
       <c r="K244" s="9" t="n">
-        <v>272.1</v>
+        <v>388.5</v>
       </c>
       <c r="L244" s="8" t="n">
-        <v>3.48</v>
+        <v>4.99</v>
       </c>
       <c r="M244" s="21" t="n">
-        <v>6802.5</v>
+        <v>9712.5</v>
       </c>
       <c r="N244" s="6" t="inlineStr">
         <is>
@@ -17452,37 +17452,37 @@
       </c>
       <c r="F260" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>13-Oct-2015 (Tue)</t>
+          <t>09-Oct-2015 (Fri)</t>
         </is>
       </c>
       <c r="H260" s="20" t="n">
-        <v>8138.8</v>
+        <v>8205.35</v>
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>26-Oct-2015 (Mon)</t>
+          <t>28-Oct-2015 (Wed)</t>
         </is>
       </c>
       <c r="J260" s="20" t="n">
-        <v>8263.6</v>
+        <v>8173.6</v>
       </c>
       <c r="K260" s="9" t="n">
-        <v>-124.8</v>
+        <v>31.75</v>
       </c>
       <c r="L260" s="8" t="n">
-        <v>-1.53</v>
+        <v>0.39</v>
       </c>
       <c r="M260" s="21" t="n">
-        <v>-3120</v>
-      </c>
-      <c r="N260" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>793.75</v>
+      </c>
+      <c r="N260" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2015-11-11</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -17568,33 +17568,33 @@
       </c>
       <c r="F262" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>05-Nov-2015 (Thu)</t>
+          <t>04-Nov-2015 (Wed)</t>
         </is>
       </c>
       <c r="H262" s="20" t="n">
-        <v>7989.4</v>
+        <v>8070.05</v>
       </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
-          <t>17-Nov-2015 (Tue)</t>
+          <t>18-Nov-2015 (Wed)</t>
         </is>
       </c>
       <c r="J262" s="20" t="n">
-        <v>7852.6</v>
+        <v>7731.95</v>
       </c>
       <c r="K262" s="9" t="n">
-        <v>-136.8</v>
+        <v>-338.1</v>
       </c>
       <c r="L262" s="8" t="n">
-        <v>-1.71</v>
+        <v>-4.19</v>
       </c>
       <c r="M262" s="21" t="n">
-        <v>-3420</v>
+        <v>-8452.5</v>
       </c>
       <c r="N262" s="17" t="inlineStr">
         <is>
@@ -18438,33 +18438,33 @@
       </c>
       <c r="F277" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G277" s="11" t="inlineStr">
         <is>
-          <t>30-Sep-2016 (Fri)</t>
+          <t>28-Sep-2016 (Wed)</t>
         </is>
       </c>
       <c r="H277" s="22" t="n">
-        <v>8640.65</v>
+        <v>8758.450000000001</v>
       </c>
       <c r="I277" s="11" t="inlineStr">
         <is>
-          <t>14-Oct-2016 (Fri)</t>
+          <t>18-Oct-2016 (Tue)</t>
         </is>
       </c>
       <c r="J277" s="22" t="n">
-        <v>8605.1</v>
+        <v>8679.85</v>
       </c>
       <c r="K277" s="15" t="n">
-        <v>35.55</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L277" s="14" t="n">
-        <v>0.41</v>
+        <v>0.9</v>
       </c>
       <c r="M277" s="23" t="n">
-        <v>888.75</v>
+        <v>1965</v>
       </c>
       <c r="N277" s="6" t="inlineStr">
         <is>
@@ -18554,33 +18554,33 @@
       </c>
       <c r="F279" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G279" s="11" t="inlineStr">
         <is>
-          <t>24-Oct-2016 (Mon)</t>
+          <t>21-Oct-2016 (Fri)</t>
         </is>
       </c>
       <c r="H279" s="22" t="n">
-        <v>8720.25</v>
+        <v>8700.35</v>
       </c>
       <c r="I279" s="11" t="inlineStr">
         <is>
-          <t>03-Nov-2016 (Thu)</t>
+          <t>04-Nov-2016 (Fri)</t>
         </is>
       </c>
       <c r="J279" s="22" t="n">
-        <v>8517.9</v>
+        <v>8458.200000000001</v>
       </c>
       <c r="K279" s="15" t="n">
-        <v>-202.35</v>
+        <v>-242.15</v>
       </c>
       <c r="L279" s="14" t="n">
-        <v>-2.32</v>
+        <v>-2.78</v>
       </c>
       <c r="M279" s="23" t="n">
-        <v>-5058.75</v>
+        <v>-6053.75</v>
       </c>
       <c r="N279" s="17" t="inlineStr">
         <is>
@@ -19366,33 +19366,33 @@
       </c>
       <c r="F293" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G293" s="11" t="inlineStr">
         <is>
-          <t>21-Sep-2017 (Thu)</t>
+          <t>19-Sep-2017 (Tue)</t>
         </is>
       </c>
       <c r="H293" s="22" t="n">
-        <v>10138.85</v>
+        <v>10168.85</v>
       </c>
       <c r="I293" s="11" t="inlineStr">
         <is>
-          <t>04-Oct-2017 (Wed)</t>
+          <t>06-Oct-2017 (Fri)</t>
         </is>
       </c>
       <c r="J293" s="22" t="n">
-        <v>9930.450000000001</v>
+        <v>10003.4</v>
       </c>
       <c r="K293" s="15" t="n">
-        <v>208.4</v>
+        <v>165.45</v>
       </c>
       <c r="L293" s="14" t="n">
-        <v>2.06</v>
+        <v>1.63</v>
       </c>
       <c r="M293" s="23" t="n">
-        <v>5210</v>
+        <v>4136.25</v>
       </c>
       <c r="N293" s="6" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>2017-10-20</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -19540,33 +19540,33 @@
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>13-Oct-2017 (Fri)</t>
+          <t>12-Oct-2017 (Thu)</t>
         </is>
       </c>
       <c r="H296" s="20" t="n">
-        <v>10192.4</v>
+        <v>10111.4</v>
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>25-Oct-2017 (Wed)</t>
+          <t>26-Oct-2017 (Thu)</t>
         </is>
       </c>
       <c r="J296" s="20" t="n">
-        <v>10289.9</v>
+        <v>10344.7</v>
       </c>
       <c r="K296" s="9" t="n">
-        <v>97.5</v>
+        <v>233.3</v>
       </c>
       <c r="L296" s="8" t="n">
-        <v>0.96</v>
+        <v>2.31</v>
       </c>
       <c r="M296" s="21" t="n">
-        <v>2437.5</v>
+        <v>5832.5</v>
       </c>
       <c r="N296" s="6" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>2018-10-19</t>
+          <t>2018-10-18</t>
         </is>
       </c>
       <c r="E312" s="17" t="inlineStr">
@@ -20468,33 +20468,33 @@
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>10-Oct-2018 (Wed)</t>
+          <t>05-Oct-2018 (Fri)</t>
         </is>
       </c>
       <c r="H312" s="20" t="n">
-        <v>10465.75</v>
+        <v>10347.15</v>
       </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2018 (Tue)</t>
+          <t>24-Oct-2018 (Wed)</t>
         </is>
       </c>
       <c r="J312" s="20" t="n">
-        <v>10147.9</v>
+        <v>10228.55</v>
       </c>
       <c r="K312" s="9" t="n">
-        <v>317.85</v>
+        <v>118.6</v>
       </c>
       <c r="L312" s="8" t="n">
-        <v>3.04</v>
+        <v>1.15</v>
       </c>
       <c r="M312" s="21" t="n">
-        <v>7946.25</v>
+        <v>2965</v>
       </c>
       <c r="N312" s="6" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="D313" s="11" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
+          <t>2018-11-07</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
@@ -20526,33 +20526,33 @@
       </c>
       <c r="F313" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G313" s="11" t="inlineStr">
         <is>
-          <t>01-Nov-2018 (Thu)</t>
+          <t>31-Oct-2018 (Wed)</t>
         </is>
       </c>
       <c r="H313" s="22" t="n">
-        <v>10413.45</v>
+        <v>10398.4</v>
       </c>
       <c r="I313" s="11" t="inlineStr">
         <is>
-          <t>13-Nov-2018 (Tue)</t>
+          <t>14-Nov-2018 (Wed)</t>
         </is>
       </c>
       <c r="J313" s="22" t="n">
-        <v>10615.95</v>
+        <v>10605</v>
       </c>
       <c r="K313" s="15" t="n">
-        <v>202.5</v>
+        <v>206.6</v>
       </c>
       <c r="L313" s="14" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="M313" s="23" t="n">
-        <v>5062.5</v>
+        <v>5165</v>
       </c>
       <c r="N313" s="6" t="inlineStr">
         <is>
@@ -21454,33 +21454,33 @@
       </c>
       <c r="F329" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G329" s="11" t="inlineStr">
         <is>
-          <t>26-Sep-2019 (Thu)</t>
+          <t>24-Sep-2019 (Tue)</t>
         </is>
       </c>
       <c r="H329" s="22" t="n">
-        <v>11569.95</v>
+        <v>11613.85</v>
       </c>
       <c r="I329" s="11" t="inlineStr">
         <is>
-          <t>10-Oct-2019 (Thu)</t>
+          <t>14-Oct-2019 (Mon)</t>
         </is>
       </c>
       <c r="J329" s="22" t="n">
-        <v>11254.25</v>
+        <v>11336.3</v>
       </c>
       <c r="K329" s="15" t="n">
-        <v>315.7</v>
+        <v>277.55</v>
       </c>
       <c r="L329" s="14" t="n">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="M329" s="23" t="n">
-        <v>7892.5</v>
+        <v>6938.75</v>
       </c>
       <c r="N329" s="6" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>2019-10-28</t>
+          <t>2019-10-27</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
@@ -21512,33 +21512,33 @@
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>18-Oct-2019 (Fri)</t>
+          <t>17-Oct-2019 (Thu)</t>
         </is>
       </c>
       <c r="H330" s="20" t="n">
-        <v>11670</v>
+        <v>11600.65</v>
       </c>
       <c r="I330" s="4" t="inlineStr">
         <is>
-          <t>31-Oct-2019 (Thu)</t>
+          <t>01-Nov-2019 (Fri)</t>
         </is>
       </c>
       <c r="J330" s="20" t="n">
-        <v>11878.95</v>
+        <v>11928.25</v>
       </c>
       <c r="K330" s="9" t="n">
-        <v>208.95</v>
+        <v>327.6</v>
       </c>
       <c r="L330" s="8" t="n">
-        <v>1.79</v>
+        <v>2.82</v>
       </c>
       <c r="M330" s="21" t="n">
-        <v>5223.75</v>
+        <v>8190</v>
       </c>
       <c r="N330" s="6" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="E346" s="17" t="inlineStr">
@@ -22440,33 +22440,33 @@
       </c>
       <c r="F346" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
         <is>
-          <t>16-Oct-2020 (Fri)</t>
+          <t>13-Oct-2020 (Tue)</t>
         </is>
       </c>
       <c r="H346" s="20" t="n">
-        <v>11765.15</v>
+        <v>11946.1</v>
       </c>
       <c r="I346" s="4" t="inlineStr">
         <is>
-          <t>28-Oct-2020 (Wed)</t>
+          <t>29-Oct-2020 (Thu)</t>
         </is>
       </c>
       <c r="J346" s="20" t="n">
-        <v>11721.5</v>
+        <v>11668.75</v>
       </c>
       <c r="K346" s="9" t="n">
-        <v>43.65</v>
+        <v>277.35</v>
       </c>
       <c r="L346" s="8" t="n">
-        <v>0.37</v>
+        <v>2.32</v>
       </c>
       <c r="M346" s="21" t="n">
-        <v>1091.25</v>
+        <v>6933.75</v>
       </c>
       <c r="N346" s="6" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
       </c>
       <c r="D347" s="11" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="E347" s="6" t="inlineStr">
@@ -22498,33 +22498,33 @@
       </c>
       <c r="F347" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G347" s="11" t="inlineStr">
         <is>
-          <t>09-Nov-2020 (Mon)</t>
+          <t>06-Nov-2020 (Fri)</t>
         </is>
       </c>
       <c r="H347" s="22" t="n">
-        <v>12467.25</v>
+        <v>12261.45</v>
       </c>
       <c r="I347" s="11" t="inlineStr">
         <is>
-          <t>19-Nov-2020 (Thu)</t>
+          <t>20-Nov-2020 (Fri)</t>
         </is>
       </c>
       <c r="J347" s="22" t="n">
-        <v>12793.5</v>
+        <v>12871.3</v>
       </c>
       <c r="K347" s="15" t="n">
-        <v>326.25</v>
+        <v>609.85</v>
       </c>
       <c r="L347" s="14" t="n">
-        <v>2.62</v>
+        <v>4.97</v>
       </c>
       <c r="M347" s="23" t="n">
-        <v>8156.25</v>
+        <v>15246.25</v>
       </c>
       <c r="N347" s="6" t="inlineStr">
         <is>
@@ -23426,33 +23426,33 @@
       </c>
       <c r="F363" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G363" s="11" t="inlineStr">
         <is>
-          <t>06-Oct-2021 (Wed)</t>
+          <t>04-Oct-2021 (Mon)</t>
         </is>
       </c>
       <c r="H363" s="22" t="n">
-        <v>17627.2</v>
+        <v>17706.25</v>
       </c>
       <c r="I363" s="11" t="inlineStr">
         <is>
-          <t>19-Oct-2021 (Tue)</t>
+          <t>21-Oct-2021 (Thu)</t>
         </is>
       </c>
       <c r="J363" s="22" t="n">
-        <v>18432.45</v>
+        <v>18202.9</v>
       </c>
       <c r="K363" s="15" t="n">
-        <v>-805.25</v>
+        <v>-496.65</v>
       </c>
       <c r="L363" s="14" t="n">
-        <v>-4.57</v>
+        <v>-2.8</v>
       </c>
       <c r="M363" s="23" t="n">
-        <v>-20131.25</v>
+        <v>-12416.25</v>
       </c>
       <c r="N363" s="17" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="E364" s="6" t="inlineStr">
@@ -23484,33 +23484,33 @@
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
         <is>
-          <t>29-Oct-2021 (Fri)</t>
+          <t>28-Oct-2021 (Thu)</t>
         </is>
       </c>
       <c r="H364" s="20" t="n">
-        <v>17715.3</v>
+        <v>17882.75</v>
       </c>
       <c r="I364" s="4" t="inlineStr">
         <is>
-          <t>10-Nov-2021 (Wed)</t>
+          <t>11-Nov-2021 (Thu)</t>
         </is>
       </c>
       <c r="J364" s="20" t="n">
-        <v>18022.95</v>
+        <v>17896.85</v>
       </c>
       <c r="K364" s="9" t="n">
-        <v>307.65</v>
+        <v>14.1</v>
       </c>
       <c r="L364" s="8" t="n">
-        <v>1.74</v>
+        <v>0.08</v>
       </c>
       <c r="M364" s="21" t="n">
-        <v>7691.25</v>
+        <v>352.5</v>
       </c>
       <c r="N364" s="6" t="inlineStr">
         <is>
@@ -24412,37 +24412,37 @@
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>26-Sep-2022 (Mon)</t>
+          <t>22-Sep-2022 (Thu)</t>
         </is>
       </c>
       <c r="H380" s="20" t="n">
-        <v>17028.75</v>
+        <v>17647.6</v>
       </c>
       <c r="I380" s="4" t="inlineStr">
         <is>
-          <t>07-Oct-2022 (Fri)</t>
+          <t>11-Oct-2022 (Tue)</t>
         </is>
       </c>
       <c r="J380" s="20" t="n">
-        <v>17328.85</v>
+        <v>16978.2</v>
       </c>
       <c r="K380" s="9" t="n">
-        <v>-300.1</v>
+        <v>669.4</v>
       </c>
       <c r="L380" s="8" t="n">
-        <v>-1.76</v>
+        <v>3.79</v>
       </c>
       <c r="M380" s="21" t="n">
-        <v>-7502.5</v>
-      </c>
-      <c r="N380" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>16735</v>
+      </c>
+      <c r="N380" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -24470,33 +24470,33 @@
       </c>
       <c r="F381" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
-          <t>18-Oct-2022 (Tue)</t>
+          <t>17-Oct-2022 (Mon)</t>
         </is>
       </c>
       <c r="H381" s="22" t="n">
-        <v>17502</v>
+        <v>17300.3</v>
       </c>
       <c r="I381" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2022 (Fri)</t>
+          <t>31-Oct-2022 (Mon)</t>
         </is>
       </c>
       <c r="J381" s="22" t="n">
-        <v>17830.2</v>
+        <v>18051.05</v>
       </c>
       <c r="K381" s="15" t="n">
-        <v>328.2</v>
+        <v>750.75</v>
       </c>
       <c r="L381" s="14" t="n">
-        <v>1.88</v>
+        <v>4.34</v>
       </c>
       <c r="M381" s="23" t="n">
-        <v>8205</v>
+        <v>18768.75</v>
       </c>
       <c r="N381" s="6" t="inlineStr">
         <is>
@@ -25398,33 +25398,33 @@
       </c>
       <c r="F397" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G397" s="11" t="inlineStr">
         <is>
-          <t>13-Oct-2023 (Fri)</t>
+          <t>11-Oct-2023 (Wed)</t>
         </is>
       </c>
       <c r="H397" s="22" t="n">
-        <v>19742.05</v>
+        <v>19850.1</v>
       </c>
       <c r="I397" s="11" t="inlineStr">
         <is>
-          <t>26-Oct-2023 (Thu)</t>
+          <t>30-Oct-2023 (Mon)</t>
         </is>
       </c>
       <c r="J397" s="22" t="n">
-        <v>18856.7</v>
+        <v>19220.9</v>
       </c>
       <c r="K397" s="15" t="n">
-        <v>885.35</v>
+        <v>629.2</v>
       </c>
       <c r="L397" s="14" t="n">
-        <v>4.48</v>
+        <v>3.17</v>
       </c>
       <c r="M397" s="23" t="n">
-        <v>22133.75</v>
+        <v>15730</v>
       </c>
       <c r="N397" s="6" t="inlineStr">
         <is>
@@ -25456,33 +25456,33 @@
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G398" s="4" t="inlineStr">
         <is>
-          <t>06-Nov-2023 (Mon)</t>
+          <t>03-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="H398" s="20" t="n">
-        <v>19486.5</v>
+        <v>19303.6</v>
       </c>
       <c r="I398" s="4" t="inlineStr">
         <is>
-          <t>16-Nov-2023 (Thu)</t>
+          <t>17-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="J398" s="20" t="n">
-        <v>19829.7</v>
+        <v>19806.5</v>
       </c>
       <c r="K398" s="9" t="n">
-        <v>343.2</v>
+        <v>502.9</v>
       </c>
       <c r="L398" s="8" t="n">
-        <v>1.76</v>
+        <v>2.61</v>
       </c>
       <c r="M398" s="21" t="n">
-        <v>8580</v>
+        <v>12572.5</v>
       </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
@@ -26384,33 +26384,33 @@
       </c>
       <c r="F414" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G414" s="4" t="inlineStr">
         <is>
-          <t>03-Oct-2024 (Thu)</t>
+          <t>30-Sep-2024 (Mon)</t>
         </is>
       </c>
       <c r="H414" s="20" t="n">
-        <v>25475.7</v>
+        <v>25990.15</v>
       </c>
       <c r="I414" s="4" t="inlineStr">
         <is>
-          <t>15-Oct-2024 (Tue)</t>
+          <t>17-Oct-2024 (Thu)</t>
         </is>
       </c>
       <c r="J414" s="20" t="n">
-        <v>25118.35</v>
+        <v>24843.8</v>
       </c>
       <c r="K414" s="9" t="n">
-        <v>357.35</v>
+        <v>1146.35</v>
       </c>
       <c r="L414" s="8" t="n">
-        <v>1.4</v>
+        <v>4.41</v>
       </c>
       <c r="M414" s="21" t="n">
-        <v>8933.75</v>
+        <v>28658.75</v>
       </c>
       <c r="N414" s="6" t="inlineStr">
         <is>
@@ -26442,33 +26442,33 @@
       </c>
       <c r="F415" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G415" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2024 (Mon)</t>
+          <t>25-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="H415" s="22" t="n">
-        <v>24348.45</v>
+        <v>24192.75</v>
       </c>
       <c r="I415" s="11" t="inlineStr">
         <is>
-          <t>06-Nov-2024 (Wed)</t>
+          <t>07-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="J415" s="22" t="n">
-        <v>24587.1</v>
+        <v>24300.5</v>
       </c>
       <c r="K415" s="15" t="n">
-        <v>238.65</v>
+        <v>107.75</v>
       </c>
       <c r="L415" s="14" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="M415" s="23" t="n">
-        <v>5966.25</v>
+        <v>2693.75</v>
       </c>
       <c r="N415" s="6" t="inlineStr">
         <is>
@@ -27370,33 +27370,33 @@
       </c>
       <c r="F431" s="11" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-8 to T+4</t>
         </is>
       </c>
       <c r="G431" s="11" t="inlineStr">
         <is>
-          <t>23-Sep-2025 (Tue)</t>
+          <t>19-Sep-2025 (Fri)</t>
         </is>
       </c>
       <c r="H431" s="22" t="n">
-        <v>25255.8</v>
+        <v>25411.2</v>
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>06-Oct-2025 (Mon)</t>
+          <t>08-Oct-2025 (Wed)</t>
         </is>
       </c>
       <c r="J431" s="22" t="n">
-        <v>25185.4</v>
+        <v>25120.4</v>
       </c>
       <c r="K431" s="15" t="n">
-        <v>70.40000000000001</v>
+        <v>290.8</v>
       </c>
       <c r="L431" s="14" t="n">
-        <v>0.28</v>
+        <v>1.14</v>
       </c>
       <c r="M431" s="23" t="n">
-        <v>1760</v>
+        <v>7270</v>
       </c>
       <c r="N431" s="6" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E432" s="6" t="inlineStr">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="F432" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="G432" s="4" t="inlineStr">
@@ -27441,20 +27441,20 @@
       </c>
       <c r="I432" s="4" t="inlineStr">
         <is>
-          <t>24-Oct-2025 (Fri)</t>
+          <t>28-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="J432" s="20" t="n">
-        <v>25814.8</v>
+        <v>25922.4</v>
       </c>
       <c r="K432" s="9" t="n">
-        <v>608.8</v>
+        <v>716.4</v>
       </c>
       <c r="L432" s="8" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="M432" s="21" t="n">
-        <v>15220</v>
+        <v>17910</v>
       </c>
       <c r="N432" s="6" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E436" s="17" t="inlineStr">
@@ -27665,28 +27665,28 @@
       </c>
       <c r="G436" s="4" t="inlineStr">
         <is>
-          <t>20-Feb-2026 (Fri)</t>
+          <t>05-Feb-2026 (Thu)</t>
         </is>
       </c>
       <c r="H436" s="20" t="n">
-        <v>25584.7</v>
+        <v>25725</v>
       </c>
       <c r="I436" s="4" t="inlineStr">
         <is>
-          <t>12-Mar-2026 (Thu)</t>
+          <t>24-Feb-2026 (Tue)</t>
         </is>
       </c>
       <c r="J436" s="20" t="n">
-        <v>23728.5</v>
+        <v>25421.7</v>
       </c>
       <c r="K436" s="9" t="n">
-        <v>1856.2</v>
+        <v>303.3</v>
       </c>
       <c r="L436" s="8" t="n">
-        <v>7.26</v>
+        <v>1.18</v>
       </c>
       <c r="M436" s="21" t="n">
-        <v>46405</v>
+        <v>7582.5</v>
       </c>
       <c r="N436" s="6" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
       </c>
       <c r="B437" s="19" t="inlineStr">
         <is>
-          <t>Good Friday</t>
+          <t>Holi Festival</t>
         </is>
       </c>
       <c r="C437" s="11" t="n">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="D437" s="11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E437" s="6" t="inlineStr">
@@ -27718,37 +27718,37 @@
       </c>
       <c r="F437" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+6</t>
         </is>
       </c>
       <c r="G437" s="11" t="inlineStr">
         <is>
-          <t>25-Mar-2026 (Wed)</t>
+          <t>27-Feb-2026 (Fri)</t>
         </is>
       </c>
       <c r="H437" s="22" t="n">
-        <v>23300</v>
+        <v>25338.6</v>
       </c>
       <c r="I437" s="11" t="inlineStr">
         <is>
-          <t>08-Apr-2026 (Wed)</t>
+          <t>11-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="J437" s="22" t="n">
-        <v>24057.8</v>
+        <v>23939.1</v>
       </c>
       <c r="K437" s="15" t="n">
-        <v>757.8</v>
+        <v>-1399.5</v>
       </c>
       <c r="L437" s="14" t="n">
-        <v>3.25</v>
+        <v>-5.52</v>
       </c>
       <c r="M437" s="23" t="n">
-        <v>18945</v>
-      </c>
-      <c r="N437" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-34987.5</v>
+      </c>
+      <c r="N437" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -27758,7 +27758,7 @@
       </c>
       <c r="B438" s="18" t="inlineStr">
         <is>
-          <t>Dr. B.R. Ambedkar Jayanti</t>
+          <t>Good Friday</t>
         </is>
       </c>
       <c r="C438" s="4" t="n">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E438" s="6" t="inlineStr">
@@ -27776,33 +27776,33 @@
       </c>
       <c r="F438" s="4" t="inlineStr">
         <is>
-          <t>T-8 to T+8</t>
+          <t>T-4 to T+3</t>
         </is>
       </c>
       <c r="G438" s="4" t="inlineStr">
         <is>
-          <t>30-Mar-2026 (Mon)</t>
+          <t>25-Mar-2026 (Wed)</t>
         </is>
       </c>
       <c r="H438" s="20" t="n">
-        <v>22318.4</v>
+        <v>23300</v>
       </c>
       <c r="I438" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026 (Fri)</t>
+          <t>08-Apr-2026 (Wed)</t>
         </is>
       </c>
       <c r="J438" s="20" t="n">
-        <v>23922.8</v>
+        <v>24057.8</v>
       </c>
       <c r="K438" s="9" t="n">
-        <v>1604.4</v>
+        <v>757.8</v>
       </c>
       <c r="L438" s="8" t="n">
-        <v>7.19</v>
+        <v>3.25</v>
       </c>
       <c r="M438" s="21" t="n">
-        <v>40110</v>
+        <v>18945</v>
       </c>
       <c r="N438" s="6" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
       </c>
       <c r="B439" s="19" t="inlineStr">
         <is>
-          <t>Maharashtra Day</t>
+          <t>Dr. B.R. Ambedkar Jayanti</t>
         </is>
       </c>
       <c r="C439" s="11" t="n">
@@ -27824,45 +27824,103 @@
       </c>
       <c r="D439" s="11" t="inlineStr">
         <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E439" s="6" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F439" s="11" t="inlineStr">
+        <is>
+          <t>T-8 to T+8</t>
+        </is>
+      </c>
+      <c r="G439" s="11" t="inlineStr">
+        <is>
+          <t>30-Mar-2026 (Mon)</t>
+        </is>
+      </c>
+      <c r="H439" s="22" t="n">
+        <v>22318.4</v>
+      </c>
+      <c r="I439" s="11" t="inlineStr">
+        <is>
+          <t>24-Apr-2026 (Fri)</t>
+        </is>
+      </c>
+      <c r="J439" s="22" t="n">
+        <v>23922.8</v>
+      </c>
+      <c r="K439" s="15" t="n">
+        <v>1604.4</v>
+      </c>
+      <c r="L439" s="14" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="M439" s="23" t="n">
+        <v>40110</v>
+      </c>
+      <c r="N439" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="20" customHeight="1">
+      <c r="A440" s="4" t="n">
+        <v>437</v>
+      </c>
+      <c r="B440" s="18" t="inlineStr">
+        <is>
+          <t>Maharashtra Day</t>
+        </is>
+      </c>
+      <c r="C440" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D440" s="4" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="E439" s="6" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F439" s="11" t="inlineStr">
+      <c r="E440" s="6" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F440" s="4" t="inlineStr">
         <is>
           <t>T-8 to T+1</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G440" s="4" t="inlineStr">
         <is>
           <t>20-Apr-2026 (Mon)</t>
         </is>
       </c>
-      <c r="H439" s="22" t="n">
+      <c r="H440" s="20" t="n">
         <v>24331.8</v>
       </c>
-      <c r="I439" s="11" t="inlineStr">
+      <c r="I440" s="4" t="inlineStr">
         <is>
           <t>04-May-2026 (Mon)</t>
         </is>
       </c>
-      <c r="J439" s="22" t="n">
+      <c r="J440" s="20" t="n">
         <v>24206</v>
       </c>
-      <c r="K439" s="15" t="n">
+      <c r="K440" s="9" t="n">
         <v>-125.8</v>
       </c>
-      <c r="L439" s="14" t="n">
+      <c r="L440" s="8" t="n">
         <v>-0.52</v>
       </c>
-      <c r="M439" s="23" t="n">
+      <c r="M440" s="21" t="n">
         <v>-3145</v>
       </c>
-      <c r="N439" s="17" t="inlineStr">
+      <c r="N440" s="17" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -27877,6 +27935,1284 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="107" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NIFTY FUTURES — GANESH CHATURTHI 26-YEAR BACKTEST AUDIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Strategy: NIFTY LONG (T-7 to T+5) · Win Rate: 88.0% · Cumulative P&amp;L: +4390.7 Points (+109,767.50 ₹/Lot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Holiday Date</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Entry Price (₹)</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Exit Price (₹)</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>Points P&amp;L</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
+          <t>Return (%)</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2001-08-22</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>09-Aug-2001 (Thu)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>1066.1</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>29-Aug-2001 (Wed)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>1069.25</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2002-09-10</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>29-Aug-2002 (Thu)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>986.6</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>17-Sep-2002 (Tue)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>989.8</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2003-08-31</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20-Aug-2003 (Wed)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>1287.8</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>05-Sep-2003 (Fri)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>1401.6</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2004-09-18</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>08-Sep-2004 (Wed)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>1650.15</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>24-Sep-2004 (Fri)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>1721.25</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2005-09-07</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>26-Aug-2005 (Fri)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>2335.55</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>14-Sep-2005 (Wed)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>2483.25</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2006-08-27</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>16-Aug-2006 (Wed)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>3349.45</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>01-Sep-2006 (Fri)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>3430.6</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2007-09-15</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>05-Sep-2007 (Wed)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>4431.9</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>21-Sep-2007 (Fri)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>4852.6</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>420.7</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2008-09-03</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>22-Aug-2008 (Fri)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>4324.1</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>10-Sep-2008 (Wed)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>4417.25</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2009-08-23</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>12-Aug-2009 (Wed)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>4460</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>28-Aug-2009 (Fri)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>4737.8</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>277.8</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>2010-09-11</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>31-Aug-2010 (Tue)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>5403.7</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>17-Sep-2010 (Fri)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>5904.05</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>500.35</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2011-09-01</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>19-Aug-2011 (Fri)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>4850.85</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>08-Sep-2011 (Thu)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>5155</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>304.15</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>2012-09-19</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>07-Sep-2012 (Fri)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>5359.1</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>26-Sep-2012 (Wed)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>5669.85</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>310.75</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2013-09-09</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>28-Aug-2013 (Wed)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>5288.95</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>16-Sep-2013 (Mon)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>5862.25</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>2014-08-29</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>19-Aug-2014 (Tue)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>7909.65</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>05-Sep-2014 (Fri)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>8116.7</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>07-Sep-2015 (Mon)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>7574.5</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>24-Sep-2015 (Thu)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>7870.35</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>295.85</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>2016-09-05</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>24-Aug-2016 (Wed)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>8654.65</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>12-Sep-2016 (Mon)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>8742.35</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2017-08-25</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>14-Aug-2017 (Mon)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>9815.6</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>01-Sep-2017 (Fri)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>10007.3</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>03-Sep-2018 (Mon)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>11641.75</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>21-Sep-2018 (Fri)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>11166.35</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-475.4</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2019-09-02</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>21-Aug-2019 (Wed)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>10932.65</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>09-Sep-2019 (Mon)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>11025.25</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>12-Aug-2020 (Wed)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>11317.8</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>28-Aug-2020 (Fri)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="n">
+        <v>11675.25</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>31-Aug-2021 (Tue)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>17122.25</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>17-Sep-2021 (Fri)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>17603.15</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>19-Aug-2022 (Fri)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>17759.5</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>07-Sep-2022 (Wed)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="n">
+        <v>17651.05</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-108.45</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>07-Sep-2023 (Thu)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>19768.7</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>26-Sep-2023 (Tue)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>19677.05</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>-91.65000000000001</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>28-Aug-2024 (Wed)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>25048.35</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>13-Sep-2024 (Fri)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>25372.6</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>T-7 to T+5</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>14-Aug-2025 (Thu)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>24684.7</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>03-Sep-2025 (Wed)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>24813.1</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27901,14 +29237,14 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY FUTURES — DIWALI (LAXMI PUJAN &amp; BALIPRATIPADA) 26-YEAR BACKTEST AUDIT</t>
+          <t>NIFTY FUTURES — CHRISTMAS &amp; YEAR-END 26-YEAR BACKTEST AUDIT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Strategy: NIFTY LONG (T-4 to T+3) · Win Rate: 88.46% · Cumulative P&amp;L: +3620.55 Points (+90,513.75 ₹/Lot)</t>
+          <t>Strategy: NIFTY LONG (T-1 to T+7) · Win Rate: 84.62% · Cumulative P&amp;L: +3927.65 Points (+98,191.25 ₹/Lot)</t>
         </is>
       </c>
     </row>
@@ -27976,7 +29312,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2000-10-27</t>
+          <t>2000-12-25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -27986,30 +29322,30 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2000 (Mon)</t>
+          <t>21-Dec-2000 (Thu)</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>1144.9</v>
+        <v>1276.55</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>01-Nov-2000 (Wed)</t>
+          <t>03-Jan-2001 (Wed)</t>
         </is>
       </c>
       <c r="H5" s="20" t="n">
-        <v>1207.6</v>
+        <v>1292.55</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>62.7</v>
+        <v>16</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>5.48</v>
+        <v>1.25</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -28023,7 +29359,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>2001-11-16</t>
+          <t>2001-12-25</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -28033,30 +29369,30 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>09-Nov-2001 (Fri)</t>
+          <t>21-Dec-2001 (Fri)</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>990.05</v>
+        <v>1051.15</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>21-Nov-2001 (Wed)</t>
+          <t>03-Jan-2002 (Thu)</t>
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>1053.85</v>
+        <v>1074.5</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>63.8</v>
+        <v>23.35</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>6.44</v>
+        <v>2.22</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -28070,7 +29406,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2002-11-06</t>
+          <t>2002-12-25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -28080,30 +29416,30 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>30-Oct-2002 (Wed)</t>
+          <t>20-Dec-2002 (Fri)</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>938.4</v>
+        <v>1078.35</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>11-Nov-2002 (Mon)</t>
+          <t>06-Jan-2003 (Mon)</t>
         </is>
       </c>
       <c r="H7" s="20" t="n">
-        <v>955.55</v>
+        <v>1084.75</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>17.15</v>
+        <v>6.4</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -28117,7 +29453,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>2003-10-27</t>
+          <t>2003-12-25</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -28127,30 +29463,30 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>21-Oct-2003 (Tue)</t>
+          <t>23-Dec-2003 (Tue)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>1510.7</v>
+        <v>1780.3</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>30-Oct-2003 (Thu)</t>
+          <t>05-Jan-2004 (Mon)</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>1517.5</v>
+        <v>1957.15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>6.8</v>
+        <v>176.85</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>0.45</v>
+        <v>9.93</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -28164,7 +29500,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2004-11-15</t>
+          <t>2004-12-25</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -28174,30 +29510,30 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>08-Nov-2004 (Mon)</t>
+          <t>23-Dec-2004 (Thu)</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>1862.05</v>
+        <v>2039.05</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>18-Nov-2004 (Thu)</t>
+          <t>04-Jan-2005 (Tue)</t>
         </is>
       </c>
       <c r="H9" s="20" t="n">
-        <v>1894.9</v>
+        <v>2108.85</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>32.85</v>
+        <v>69.8</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1.76</v>
+        <v>3.42</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
@@ -28211,7 +29547,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>2005-11-03</t>
+          <t>2005-12-25</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -28221,30 +29557,30 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>27-Oct-2005 (Thu)</t>
+          <t>22-Dec-2005 (Thu)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>2361.1</v>
+        <v>2830.65</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>09-Nov-2005 (Wed)</t>
+          <t>03-Jan-2006 (Tue)</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>2480.75</v>
+        <v>2868.85</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>119.65</v>
+        <v>38.2</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>5.07</v>
+        <v>1.35</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -28258,7 +29594,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2006-10-24</t>
+          <t>2006-12-25</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -28268,30 +29604,30 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>17-Oct-2006 (Tue)</t>
+          <t>21-Dec-2006 (Thu)</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>3719.1</v>
+        <v>3815.65</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>30-Oct-2006 (Mon)</t>
+          <t>04-Jan-2007 (Thu)</t>
         </is>
       </c>
       <c r="H11" s="20" t="n">
-        <v>3775.1</v>
+        <v>3986.3</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>56</v>
+        <v>170.65</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>1.51</v>
+        <v>4.47</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -28305,7 +29641,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>2007-11-12</t>
+          <t>2007-12-25</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -28315,30 +29651,30 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>06-Nov-2007 (Tue)</t>
+          <t>20-Dec-2007 (Thu)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>5802.25</v>
+        <v>5789.55</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>15-Nov-2007 (Thu)</t>
+          <t>03-Jan-2008 (Thu)</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>5915.9</v>
+        <v>6178.2</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>113.65</v>
+        <v>388.65</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1.96</v>
+        <v>6.71</v>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
@@ -28352,7 +29688,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2008-10-30</t>
+          <t>2008-12-25</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -28362,30 +29698,30 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2008 (Thu)</t>
+          <t>23-Dec-2008 (Tue)</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>2934.7</v>
+        <v>2972.85</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>04-Nov-2008 (Tue)</t>
+          <t>05-Jan-2009 (Mon)</t>
         </is>
       </c>
       <c r="H13" s="20" t="n">
-        <v>3161.9</v>
+        <v>3122.25</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>227.2</v>
+        <v>149.4</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>7.74</v>
+        <v>5.03</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -28399,7 +29735,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>2009-10-19</t>
+          <t>2009-12-25</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -28409,30 +29745,30 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>09-Oct-2009 (Fri)</t>
+          <t>23-Dec-2009 (Wed)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>4934.5</v>
+        <v>5156.85</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>22-Oct-2009 (Thu)</t>
+          <t>07-Jan-2010 (Thu)</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>4997.4</v>
+        <v>5266.35</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>62.9</v>
+        <v>109.5</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -28446,7 +29782,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2010-11-05</t>
+          <t>2010-12-25</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -28456,30 +29792,30 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>01-Nov-2010 (Mon)</t>
+          <t>23-Dec-2010 (Thu)</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>6152.05</v>
+        <v>5996.15</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>10-Nov-2010 (Wed)</t>
+          <t>04-Jan-2011 (Tue)</t>
         </is>
       </c>
       <c r="H15" s="20" t="n">
-        <v>6308.3</v>
+        <v>6160.1</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>156.25</v>
+        <v>163.95</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -28493,7 +29829,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>2011-10-27</t>
+          <t>2011-12-25</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -28503,30 +29839,30 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>20-Oct-2011 (Thu)</t>
+          <t>22-Dec-2011 (Thu)</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>5102.85</v>
+        <v>4748.9</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>01-Nov-2011 (Tue)</t>
+          <t>03-Jan-2012 (Tue)</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>5291.4</v>
+        <v>4783.2</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>188.55</v>
+        <v>34.3</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.69</v>
+        <v>0.72</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -28540,7 +29876,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2012-11-14</t>
+          <t>2012-12-25</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -28550,34 +29886,34 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>07-Nov-2012 (Wed)</t>
+          <t>21-Dec-2012 (Fri)</t>
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>5793.25</v>
+        <v>5853.4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>19-Nov-2012 (Mon)</t>
+          <t>03-Jan-2013 (Thu)</t>
         </is>
       </c>
       <c r="H17" s="20" t="n">
-        <v>5589.65</v>
+        <v>6039.55</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-203.6</v>
+        <v>186.15</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>3.18</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -28587,7 +29923,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
+          <t>2013-12-25</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -28597,34 +29933,34 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2013 (Mon)</t>
+          <t>23-Dec-2013 (Mon)</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>6105.3</v>
+        <v>6302.35</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>07-Nov-2013 (Thu)</t>
+          <t>03-Jan-2014 (Fri)</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>6227.3</v>
+        <v>6251.75</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>122</v>
+        <v>-50.6</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-0.8</v>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -28634,7 +29970,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2014-12-25</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -28644,30 +29980,30 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>17-Oct-2014 (Fri)</t>
+          <t>23-Dec-2014 (Tue)</t>
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>7817.05</v>
+        <v>8271.549999999999</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>29-Oct-2014 (Wed)</t>
+          <t>05-Jan-2015 (Mon)</t>
         </is>
       </c>
       <c r="H19" s="20" t="n">
-        <v>8089.15</v>
+        <v>8422.85</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>272.1</v>
+        <v>151.3</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>3.48</v>
+        <v>1.83</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
@@ -28681,7 +30017,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2015-12-25</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -28691,30 +30027,30 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>05-Nov-2015 (Thu)</t>
+          <t>23-Dec-2015 (Wed)</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>7989.4</v>
+        <v>7864</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>17-Nov-2015 (Tue)</t>
+          <t>05-Jan-2016 (Tue)</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>7852.6</v>
+        <v>7802.75</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-136.8</v>
+        <v>-61.25</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>-1.71</v>
+        <v>-0.78</v>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
@@ -28728,7 +30064,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
+          <t>2016-12-25</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -28738,34 +30074,34 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>24-Oct-2016 (Mon)</t>
+          <t>22-Dec-2016 (Thu)</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>8720.25</v>
+        <v>7996.85</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>03-Nov-2016 (Thu)</t>
+          <t>03-Jan-2017 (Tue)</t>
         </is>
       </c>
       <c r="H21" s="20" t="n">
-        <v>8517.9</v>
+        <v>8196.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-202.35</v>
+        <v>199.65</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>2.5</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -28775,7 +30111,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>2017-10-20</t>
+          <t>2017-12-25</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -28785,30 +30121,30 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>13-Oct-2017 (Fri)</t>
+          <t>21-Dec-2017 (Thu)</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>10192.4</v>
+        <v>10462.45</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>25-Oct-2017 (Wed)</t>
+          <t>03-Jan-2018 (Wed)</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>10289.9</v>
+        <v>10469.4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>97.5</v>
+        <v>6.95</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
@@ -28822,7 +30158,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
+          <t>2018-12-25</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -28832,34 +30168,34 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>01-Nov-2018 (Thu)</t>
+          <t>21-Dec-2018 (Fri)</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>10413.45</v>
+        <v>10767.5</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>13-Nov-2018 (Tue)</t>
+          <t>03-Jan-2019 (Thu)</t>
         </is>
       </c>
       <c r="H23" s="20" t="n">
-        <v>10615.95</v>
+        <v>10718.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>202.5</v>
+        <v>-49</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-0.46</v>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -28869,7 +30205,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>2019-10-28</t>
+          <t>2019-12-25</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -28879,34 +30215,34 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>18-Oct-2019 (Fri)</t>
+          <t>23-Dec-2019 (Mon)</t>
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>11670</v>
+        <v>12276.45</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>31-Oct-2019 (Thu)</t>
+          <t>03-Jan-2020 (Fri)</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>11878.95</v>
+        <v>12256.45</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>208.95</v>
+        <v>-20</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-0.16</v>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -28916,7 +30252,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -28926,30 +30262,30 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>09-Nov-2020 (Mon)</t>
+          <t>23-Dec-2020 (Wed)</t>
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>12467.25</v>
+        <v>13612.45</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>19-Nov-2020 (Thu)</t>
+          <t>05-Jan-2021 (Tue)</t>
         </is>
       </c>
       <c r="H25" s="20" t="n">
-        <v>12793.5</v>
+        <v>14217.95</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>326.25</v>
+        <v>605.5</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>2.62</v>
+        <v>4.45</v>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
@@ -28963,7 +30299,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -28973,30 +30309,30 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2021 (Fri)</t>
+          <t>23-Dec-2021 (Thu)</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>17715.3</v>
+        <v>17078.45</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>10-Nov-2021 (Wed)</t>
+          <t>04-Jan-2022 (Tue)</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>18022.95</v>
+        <v>17846.75</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>307.65</v>
+        <v>768.3</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>1.74</v>
+        <v>4.5</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
@@ -29010,7 +30346,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -29020,30 +30356,30 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>18-Oct-2022 (Tue)</t>
+          <t>22-Dec-2022 (Thu)</t>
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>17502</v>
+        <v>18170.35</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>28-Oct-2022 (Fri)</t>
+          <t>03-Jan-2023 (Tue)</t>
         </is>
       </c>
       <c r="H27" s="20" t="n">
-        <v>17830.2</v>
+        <v>18317.3</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>328.2</v>
+        <v>146.95</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
@@ -29057,7 +30393,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -29067,30 +30403,30 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>06-Nov-2023 (Mon)</t>
+          <t>21-Dec-2023 (Thu)</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>19486.5</v>
+        <v>21350.4</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>16-Nov-2023 (Thu)</t>
+          <t>03-Jan-2024 (Wed)</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>19829.7</v>
+        <v>21600</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>343.2</v>
+        <v>249.6</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>1.76</v>
+        <v>1.17</v>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
@@ -29104,7 +30440,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -29114,30 +30450,30 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>28-Oct-2024 (Mon)</t>
+          <t>23-Dec-2024 (Mon)</t>
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>24348.45</v>
+        <v>23769.75</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>06-Nov-2024 (Wed)</t>
+          <t>03-Jan-2025 (Fri)</t>
         </is>
       </c>
       <c r="H29" s="20" t="n">
-        <v>24587.1</v>
+        <v>24092.4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>238.65</v>
+        <v>322.65</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.98</v>
+        <v>1.36</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
@@ -29151,7 +30487,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -29161,1310 +30497,32 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>14-Oct-2025 (Tue)</t>
+          <t>23-Dec-2025 (Tue)</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>25206</v>
+        <v>26206.9</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>24-Oct-2025 (Fri)</t>
+          <t>05-Jan-2026 (Mon)</t>
         </is>
       </c>
       <c r="H30" s="22" t="n">
-        <v>25814.8</v>
+        <v>26331.3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>608.8</v>
+        <v>124.4</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>2.42</v>
+        <v>0.47</v>
       </c>
       <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="107" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NIFTY FUTURES — GANESH CHATURTHI 26-YEAR BACKTEST AUDIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Strategy: NIFTY LONG (T-7 to T+5) · Win Rate: 88.0% · Cumulative P&amp;L: +4390.7 Points (+109,767.50 ₹/Lot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Holiday Date</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>Entry Price (₹)</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>Exit Date</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>Exit Price (₹)</t>
-        </is>
-      </c>
-      <c r="I4" s="25" t="inlineStr">
-        <is>
-          <t>Points P&amp;L</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
-        <is>
-          <t>Return (%)</t>
-        </is>
-      </c>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2001-08-22</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>09-Aug-2001 (Thu)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>1066.1</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>29-Aug-2001 (Wed)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>1069.25</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>2002-09-10</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>29-Aug-2002 (Thu)</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>986.6</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>17-Sep-2002 (Tue)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>989.8</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2003-08-31</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>20-Aug-2003 (Wed)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>1287.8</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>05-Sep-2003 (Fri)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="n">
-        <v>1401.6</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>2004-09-18</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>08-Sep-2004 (Wed)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>1650.15</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>24-Sep-2004 (Fri)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>1721.25</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2005-09-07</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>26-Aug-2005 (Fri)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>2335.55</v>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>14-Sep-2005 (Wed)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>2483.25</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>147.7</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="11" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>2006-08-27</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>16-Aug-2006 (Wed)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>3349.45</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>01-Sep-2006 (Fri)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>3430.6</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>81.15000000000001</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2007-09-15</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>05-Sep-2007 (Wed)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>4431.9</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>21-Sep-2007 (Fri)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>4852.6</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>420.7</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>2008-09-03</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>22-Aug-2008 (Fri)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>4324.1</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>10-Sep-2008 (Wed)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>4417.25</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>93.15000000000001</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2009-08-23</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2009 (Wed)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>4460</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>28-Aug-2009 (Fri)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>4737.8</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>277.8</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>2010-09-11</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>31-Aug-2010 (Tue)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>5403.7</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>17-Sep-2010 (Fri)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>5904.05</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>500.35</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>2011-09-01</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2011 (Fri)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="n">
-        <v>4850.85</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>08-Sep-2011 (Thu)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>5155</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>304.15</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>2012-09-19</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>07-Sep-2012 (Fri)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>5359.1</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>26-Sep-2012 (Wed)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>5669.85</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>310.75</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2013-09-09</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>28-Aug-2013 (Wed)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="n">
-        <v>5288.95</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>16-Sep-2013 (Mon)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>5862.25</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>573.3</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>2014-08-29</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>19-Aug-2014 (Tue)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>7909.65</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>05-Sep-2014 (Fri)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>8116.7</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>207.05</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2015-09-17</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>07-Sep-2015 (Mon)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>7574.5</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>24-Sep-2015 (Thu)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>7870.35</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>295.85</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>2016-09-05</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>24-Aug-2016 (Wed)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>8654.65</v>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>12-Sep-2016 (Mon)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>8742.35</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2017-08-25</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>14-Aug-2017 (Mon)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>9815.6</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>01-Sep-2017 (Fri)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="n">
-        <v>10007.3</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>191.7</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>03-Sep-2018 (Mon)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="n">
-        <v>11641.75</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>21-Sep-2018 (Fri)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="n">
-        <v>11166.35</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>-475.4</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2019-09-02</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>21-Aug-2019 (Wed)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>10932.65</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>09-Sep-2019 (Mon)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>11025.25</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="11" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>2020-08-22</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>12-Aug-2020 (Wed)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="n">
-        <v>11317.8</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>28-Aug-2020 (Fri)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="n">
-        <v>11675.25</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>357.45</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>31-Aug-2021 (Tue)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>17122.25</v>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>17-Sep-2021 (Fri)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>17603.15</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>480.9</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>19-Aug-2022 (Fri)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>17759.5</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>07-Sep-2022 (Wed)</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="n">
-        <v>17651.05</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>-108.45</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>07-Sep-2023 (Thu)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>19768.7</v>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>26-Sep-2023 (Tue)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>19677.05</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>-91.65000000000001</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>28-Aug-2024 (Wed)</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="n">
-        <v>25048.35</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>13-Sep-2024 (Fri)</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="n">
-        <v>25372.6</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>324.25</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>T-7 to T+5</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>14-Aug-2025 (Thu)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>24684.7</v>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>03-Sep-2025 (Wed)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="n">
-        <v>24813.1</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>128.4</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -30504,14 +30562,14 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY FUTURES — CHRISTMAS &amp; YEAR-END 26-YEAR BACKTEST AUDIT</t>
+          <t>NIFTY FUTURES — DIWALI (LAXMI PUJAN &amp; BALIPRATIPADA) 26-YEAR BACKTEST AUDIT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Strategy: NIFTY LONG (T-1 to T+7) · Win Rate: 84.62% · Cumulative P&amp;L: +3927.65 Points (+98,191.25 ₹/Lot)</t>
+          <t>Strategy: NIFTY LONG (T-5 to T+4) · Win Rate: 84.62% · Cumulative P&amp;L: +3838.85 Points (+95,971.25 ₹/Lot)</t>
         </is>
       </c>
     </row>
@@ -30579,7 +30637,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2000-12-25</t>
+          <t>2000-10-27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -30589,30 +30647,30 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>21-Dec-2000 (Thu)</t>
+          <t>20-Oct-2000 (Fri)</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>1276.55</v>
+        <v>1138.85</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2001 (Wed)</t>
+          <t>02-Nov-2000 (Thu)</t>
         </is>
       </c>
       <c r="H5" s="20" t="n">
-        <v>1292.55</v>
+        <v>1230.8</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>16</v>
+        <v>91.95</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1.25</v>
+        <v>8.07</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -30626,7 +30684,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>2001-12-25</t>
+          <t>2001-11-16</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -30636,30 +30694,30 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>21-Dec-2001 (Fri)</t>
+          <t>08-Nov-2001 (Thu)</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>1051.15</v>
+        <v>988.3</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2002 (Thu)</t>
+          <t>22-Nov-2001 (Thu)</t>
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>1074.5</v>
+        <v>1057.5</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>23.35</v>
+        <v>69.2</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -30673,7 +30731,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2002-12-25</t>
+          <t>2002-11-04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -30683,30 +30741,30 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>20-Dec-2002 (Fri)</t>
+          <t>28-Oct-2002 (Mon)</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>1078.35</v>
+        <v>927.7</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>06-Jan-2003 (Mon)</t>
+          <t>11-Nov-2002 (Mon)</t>
         </is>
       </c>
       <c r="H7" s="20" t="n">
-        <v>1084.75</v>
+        <v>955.55</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>6.4</v>
+        <v>27.85</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.59</v>
+        <v>3</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -30720,7 +30778,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>2003-12-25</t>
+          <t>2003-10-27</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -30730,30 +30788,30 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2003 (Tue)</t>
+          <t>20-Oct-2003 (Mon)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>1780.3</v>
+        <v>1541.4</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>05-Jan-2004 (Mon)</t>
+          <t>31-Oct-2003 (Fri)</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>1957.15</v>
+        <v>1559.45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>176.85</v>
+        <v>18.05</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>9.93</v>
+        <v>1.17</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -30767,7 +30825,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2004-12-25</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -30777,30 +30835,30 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2004 (Thu)</t>
+          <t>05-Nov-2004 (Fri)</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>2039.05</v>
+        <v>1856.8</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>04-Jan-2005 (Tue)</t>
+          <t>19-Nov-2004 (Fri)</t>
         </is>
       </c>
       <c r="H9" s="20" t="n">
-        <v>2108.85</v>
+        <v>1871.3</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>69.8</v>
+        <v>14.5</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3.42</v>
+        <v>0.78</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
@@ -30814,7 +30872,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>2005-12-25</t>
+          <t>2005-11-03</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -30824,30 +30882,30 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>22-Dec-2005 (Thu)</t>
+          <t>26-Oct-2005 (Wed)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>2830.65</v>
+        <v>2413.65</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2006 (Tue)</t>
+          <t>10-Nov-2005 (Thu)</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>2868.85</v>
+        <v>2489.95</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>38.2</v>
+        <v>76.3</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>1.35</v>
+        <v>3.16</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -30861,7 +30919,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2006-12-25</t>
+          <t>2006-10-21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -30871,30 +30929,30 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>21-Dec-2006 (Thu)</t>
+          <t>13-Oct-2006 (Fri)</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>3815.65</v>
+        <v>3678.4</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>04-Jan-2007 (Thu)</t>
+          <t>30-Oct-2006 (Mon)</t>
         </is>
       </c>
       <c r="H11" s="20" t="n">
-        <v>3986.3</v>
+        <v>3775.1</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>170.65</v>
+        <v>96.7</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>4.47</v>
+        <v>2.63</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -30908,7 +30966,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>2007-12-25</t>
+          <t>2007-11-12</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -30918,30 +30976,30 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>20-Dec-2007 (Thu)</t>
+          <t>05-Nov-2007 (Mon)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>5789.55</v>
+        <v>5844.9</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2008 (Thu)</t>
+          <t>16-Nov-2007 (Fri)</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>6178.2</v>
+        <v>5913.55</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>388.65</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>6.71</v>
+        <v>1.17</v>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
@@ -30955,7 +31013,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2008-12-25</t>
+          <t>2008-10-28</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -30965,34 +31023,34 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2008 (Tue)</t>
+          <t>21-Oct-2008 (Tue)</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>2972.85</v>
+        <v>3241.95</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>05-Jan-2009 (Mon)</t>
+          <t>04-Nov-2008 (Tue)</t>
         </is>
       </c>
       <c r="H13" s="20" t="n">
-        <v>3122.25</v>
+        <v>3161.9</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>149.4</v>
+        <v>-80.05</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-2.47</v>
+      </c>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -31002,7 +31060,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>2009-12-25</t>
+          <t>2009-10-19</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -31012,30 +31070,30 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2009 (Wed)</t>
+          <t>08-Oct-2009 (Thu)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>5156.85</v>
+        <v>5001.7</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>07-Jan-2010 (Thu)</t>
+          <t>23-Oct-2009 (Fri)</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>5266.35</v>
+        <v>5007.9</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>109.5</v>
+        <v>6.2</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>2.12</v>
+        <v>0.12</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -31049,7 +31107,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2010-12-25</t>
+          <t>2010-11-05</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -31059,30 +31117,30 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2010 (Thu)</t>
+          <t>29-Oct-2010 (Fri)</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>5996.15</v>
+        <v>6043.6</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>04-Jan-2011 (Tue)</t>
+          <t>11-Nov-2010 (Thu)</t>
         </is>
       </c>
       <c r="H15" s="20" t="n">
-        <v>6160.1</v>
+        <v>6232.55</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>163.95</v>
+        <v>188.95</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>2.73</v>
+        <v>3.13</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -31096,7 +31154,7 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>2011-12-25</t>
+          <t>2011-10-27</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -31106,30 +31164,30 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>22-Dec-2011 (Thu)</t>
+          <t>19-Oct-2011 (Wed)</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>4748.9</v>
+        <v>5149.4</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2012 (Tue)</t>
+          <t>02-Nov-2011 (Wed)</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>4783.2</v>
+        <v>5280.2</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>34.3</v>
+        <v>130.8</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>0.72</v>
+        <v>2.54</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -31143,7 +31201,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2012-12-25</t>
+          <t>2012-11-13</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -31153,34 +31211,34 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>21-Dec-2012 (Fri)</t>
+          <t>06-Nov-2012 (Tue)</t>
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>5853.4</v>
+        <v>5766.65</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2013 (Thu)</t>
+          <t>20-Nov-2012 (Tue)</t>
         </is>
       </c>
       <c r="H17" s="20" t="n">
-        <v>6039.55</v>
+        <v>5583.85</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>186.15</v>
+        <v>-182.8</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-3.17</v>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -31190,7 +31248,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>2013-12-25</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -31200,34 +31258,34 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2013 (Mon)</t>
+          <t>25-Oct-2013 (Fri)</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>6302.35</v>
+        <v>6151.55</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2014 (Fri)</t>
+          <t>08-Nov-2013 (Fri)</t>
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>6251.75</v>
+        <v>6186.6</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-50.6</v>
+        <v>35.05</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>0.57</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31295,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2014-12-25</t>
+          <t>2014-10-23</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -31247,30 +31305,30 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2014 (Tue)</t>
+          <t>16-Oct-2014 (Thu)</t>
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>8271.549999999999</v>
+        <v>7778.1</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>05-Jan-2015 (Mon)</t>
+          <t>30-Oct-2014 (Thu)</t>
         </is>
       </c>
       <c r="H19" s="20" t="n">
-        <v>8422.85</v>
+        <v>8166.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>151.3</v>
+        <v>388.5</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>1.83</v>
+        <v>4.99</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
@@ -31284,7 +31342,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>2015-12-25</t>
+          <t>2015-11-11</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -31294,30 +31352,30 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2015 (Wed)</t>
+          <t>04-Nov-2015 (Wed)</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>7864</v>
+        <v>8070.05</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>05-Jan-2016 (Tue)</t>
+          <t>18-Nov-2015 (Wed)</t>
         </is>
       </c>
       <c r="H20" s="22" t="n">
-        <v>7802.75</v>
+        <v>7731.95</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-61.25</v>
+        <v>-338.1</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>-0.78</v>
+        <v>-4.19</v>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
@@ -31331,7 +31389,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2016-12-25</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -31341,34 +31399,34 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>22-Dec-2016 (Thu)</t>
+          <t>21-Oct-2016 (Fri)</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>7996.85</v>
+        <v>8700.35</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2017 (Tue)</t>
+          <t>04-Nov-2016 (Fri)</t>
         </is>
       </c>
       <c r="H21" s="20" t="n">
-        <v>8196.5</v>
+        <v>8458.200000000001</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>199.65</v>
+        <v>-242.15</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-2.78</v>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -31378,7 +31436,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>2017-12-25</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -31388,30 +31446,30 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>21-Dec-2017 (Thu)</t>
+          <t>12-Oct-2017 (Thu)</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>10462.45</v>
+        <v>10111.4</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2018 (Wed)</t>
+          <t>26-Oct-2017 (Thu)</t>
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>10469.4</v>
+        <v>10344.7</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>6.95</v>
+        <v>233.3</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.31</v>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
@@ -31425,7 +31483,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2018-12-25</t>
+          <t>2018-11-07</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -31435,34 +31493,34 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>21-Dec-2018 (Fri)</t>
+          <t>31-Oct-2018 (Wed)</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>10767.5</v>
+        <v>10398.4</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2019 (Thu)</t>
+          <t>14-Nov-2018 (Wed)</t>
         </is>
       </c>
       <c r="H23" s="20" t="n">
-        <v>10718.5</v>
+        <v>10605</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-49</v>
+        <v>206.6</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>1.99</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31472,7 +31530,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>2019-12-25</t>
+          <t>2019-10-27</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -31482,34 +31540,34 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2019 (Mon)</t>
+          <t>17-Oct-2019 (Thu)</t>
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>12276.45</v>
+        <v>11600.65</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2020 (Fri)</t>
+          <t>01-Nov-2019 (Fri)</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>12256.45</v>
+        <v>11928.25</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-20</v>
+        <v>327.6</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>2.82</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31519,7 +31577,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -31529,30 +31587,30 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2020 (Wed)</t>
+          <t>06-Nov-2020 (Fri)</t>
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>13612.45</v>
+        <v>12261.45</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>05-Jan-2021 (Tue)</t>
+          <t>20-Nov-2020 (Fri)</t>
         </is>
       </c>
       <c r="H25" s="20" t="n">
-        <v>14217.95</v>
+        <v>12871.3</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>605.5</v>
+        <v>609.85</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>4.45</v>
+        <v>4.97</v>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
@@ -31566,7 +31624,7 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-11-04</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -31576,30 +31634,30 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2021 (Thu)</t>
+          <t>28-Oct-2021 (Thu)</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>17078.45</v>
+        <v>17882.75</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>04-Jan-2022 (Tue)</t>
+          <t>11-Nov-2021 (Thu)</t>
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>17846.75</v>
+        <v>17896.85</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>768.3</v>
+        <v>14.1</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>4.5</v>
+        <v>0.08</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
@@ -31613,7 +31671,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -31623,30 +31681,30 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>22-Dec-2022 (Thu)</t>
+          <t>17-Oct-2022 (Mon)</t>
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>18170.35</v>
+        <v>17300.3</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2023 (Tue)</t>
+          <t>31-Oct-2022 (Mon)</t>
         </is>
       </c>
       <c r="H27" s="20" t="n">
-        <v>18317.3</v>
+        <v>18051.05</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>146.95</v>
+        <v>750.75</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
@@ -31660,7 +31718,7 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -31670,30 +31728,30 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>21-Dec-2023 (Thu)</t>
+          <t>03-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>21350.4</v>
+        <v>19303.6</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>03-Jan-2024 (Wed)</t>
+          <t>17-Nov-2023 (Fri)</t>
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>21600</v>
+        <v>19806.5</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>249.6</v>
+        <v>502.9</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>1.17</v>
+        <v>2.61</v>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
@@ -31707,7 +31765,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -31717,30 +31775,30 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>23-Dec-2024 (Mon)</t>
+          <t>25-Oct-2024 (Fri)</t>
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>23769.75</v>
+        <v>24192.75</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>03-Jan-2025 (Fri)</t>
+          <t>07-Nov-2024 (Thu)</t>
         </is>
       </c>
       <c r="H29" s="20" t="n">
-        <v>24092.4</v>
+        <v>24300.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>322.65</v>
+        <v>107.75</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1.36</v>
+        <v>0.45</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
@@ -31754,7 +31812,7 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -31764,30 +31822,30 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>T-1 to T+7</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>23-Dec-2025 (Tue)</t>
+          <t>14-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>26206.9</v>
+        <v>25206</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>05-Jan-2026 (Mon)</t>
+          <t>28-Oct-2025 (Tue)</t>
         </is>
       </c>
       <c r="H30" s="22" t="n">
-        <v>26331.3</v>
+        <v>25922.4</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>124.4</v>
+        <v>716.4</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>0.47</v>
+        <v>2.84</v>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
